--- a/docs/tabulka-hnev.xlsx
+++ b/docs/tabulka-hnev.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vutbr-my.sharepoint.com/personal/267991_vutbr_cz/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kajik BP web\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAE17215-0449-428A-A635-BE990E71E21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC9BD7C-900D-4CFC-8F13-C07042DF0E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8585123D-28A0-4BD2-87B7-9BF3FF211F10}"/>
   </bookViews>
@@ -39,49 +39,305 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>Jsem naštvaný</t>
-  </si>
-  <si>
-    <t>Tohle mě štve</t>
-  </si>
-  <si>
-    <t>Nemůžu to už poslouchat</t>
-  </si>
-  <si>
-    <t>Tohle mě rozčiluje</t>
-  </si>
-  <si>
-    <t>Dochází mi trpělivost</t>
-  </si>
-  <si>
-    <t>Vůbec se mi to nelíbí</t>
-  </si>
-  <si>
-    <t>Mám toho plné zuby</t>
-  </si>
-  <si>
-    <t>Nemám na to nervy</t>
-  </si>
-  <si>
-    <t>Je to naprostá drzost</t>
-  </si>
-  <si>
-    <t>Teď jsi mě naštval</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>Jsem/. na/. štva/. ný/-</t>
+  </si>
+  <si>
+    <t>To/. hle/. mě/. štve.</t>
+  </si>
+  <si>
+    <t>Do/. chá/- zí/- mi/. tr/. pě/. li/. vost/.</t>
+  </si>
+  <si>
+    <t>Vů/- bec/. se/. mi/. to/. ne/. lí/- bí/-</t>
+  </si>
+  <si>
+    <t>Mám/- to/. ho/. pl/. né/- zu/. by/.</t>
+  </si>
+  <si>
+    <t>Ne/. mám/- na/. to/. ner/. vy/.</t>
+  </si>
+  <si>
+    <t>Teď/. jsi/. mě/. naš/. tval/.</t>
+  </si>
+  <si>
+    <t>Tak/. to/. ne/.</t>
+  </si>
+  <si>
+    <t>To/. je/. a/. le/. dr/. zost/.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ne/. mů/- žu/. to/. a/. ni/. po/. slou/. chat/. </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jsem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> naštvaný</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tohle </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mě</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> štve</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nemůžu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to ani poslouchat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tak</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to ne</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dochází </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trpělivost</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vůbec</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> se mi to nelíbí</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mám toho plné </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>zuby</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nemám</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> na to nervy</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">To je </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> drzost</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Teď</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> jsi mě naštval</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -105,8 +361,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -441,57 +698,90 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1573F9AA-7AF3-4CF1-B95D-8116BD420614}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/tabulka-hnev.xlsx
+++ b/docs/tabulka-hnev.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kajik BP web\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kajik BP web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC9BD7C-900D-4CFC-8F13-C07042DF0E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66008CA0-BB33-499C-B510-E6E268027F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8585123D-28A0-4BD2-87B7-9BF3FF211F10}"/>
+    <workbookView xWindow="-18720" yWindow="3765" windowWidth="21600" windowHeight="11385" xr2:uid="{8585123D-28A0-4BD2-87B7-9BF3FF211F10}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -701,7 +701,7 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
